--- a/حسابداری/بانک ها/ملت/1405/14050201-14050220.xlsx
+++ b/حسابداری/بانک ها/ملت/1405/14050201-14050220.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\بانک ها\ملت\1405\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\ملت\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B55612-0B8A-4228-A5F3-ACE0E80D1018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8675B98-0FAB-401A-A857-4D3EAF9653D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>کارمزد ۱ حواله سرجمع خرید شاپرک</t>
   </si>
@@ -118,13 +118,25 @@
   </si>
   <si>
     <t>کارمزد</t>
+  </si>
+  <si>
+    <t>حواله شاپرک ۰۵۰۲۲۷۰۳۱۱۰۰۰۰۰۰۰۰۴۲</t>
+  </si>
+  <si>
+    <t>1405/02/28</t>
+  </si>
+  <si>
+    <t>حواله شاپرک ۰۵۰۲۳۰۰۳۱۱۰۰۰۰۰۰۰۰۴۲</t>
+  </si>
+  <si>
+    <t>1405/02/31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,6 +148,12 @@
       <sz val="11"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -194,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -208,10 +226,13 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="19" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -494,12 +515,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.75" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.375" style="1" bestFit="1" customWidth="1"/>
@@ -720,7 +740,193 @@
         <v>30</v>
       </c>
     </row>
+    <row r="5" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.18361111111111111</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4481</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2193965</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>82000000</v>
+      </c>
+      <c r="L5" s="2">
+        <v>238268182</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+    </row>
+    <row r="6" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.21354166666666666</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1503</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>126341577</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>16400</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>238251782</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2">
+        <v>16400</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.19012731481481482</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4481</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2329735</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1100000</v>
+      </c>
+      <c r="L7" s="2">
+        <v>239351782</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.22421296296296298</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1503</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>127947617</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1200</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>239350582</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+    </row>
+    <row r="11" spans="1:20" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/حسابداری/بانک ها/ملت/1405/14050201-14050220.xlsx
+++ b/حسابداری/بانک ها/ملت/1405/14050201-14050220.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\ملت\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8675B98-0FAB-401A-A857-4D3EAF9653D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3545F1D3-DACE-4EEC-B4C1-F511C9F5BE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>کارمزد ۱ حواله سرجمع خرید شاپرک</t>
   </si>
   <si>
-    <t>اداره کل مدیریت عملیات</t>
-  </si>
-  <si>
     <t>1405/02/16</t>
   </si>
   <si>
@@ -42,18 +39,12 @@
     <t>پذیرنده ۴۲۳۹۱۵۱</t>
   </si>
   <si>
-    <t>اداره امور پایا</t>
-  </si>
-  <si>
     <t>حواله همراه بانک بابت  ۱۲۸۷۲۷۵۹۳۳</t>
   </si>
   <si>
     <t>محمد تهرانی معتمد</t>
   </si>
   <si>
-    <t>اداره حسابداری متمرکز</t>
-  </si>
-  <si>
     <t>1405/02/08</t>
   </si>
   <si>
@@ -72,18 +63,6 @@
     <t>واریز کننده/ ذیتفع</t>
   </si>
   <si>
-    <t>شماره سریال</t>
-  </si>
-  <si>
-    <t>شناسه واریز</t>
-  </si>
-  <si>
-    <t>کد حسابگری</t>
-  </si>
-  <si>
-    <t>شعبه</t>
-  </si>
-  <si>
     <t>زمان</t>
   </si>
   <si>
@@ -130,13 +109,38 @@
   </si>
   <si>
     <t>1405/02/31</t>
+  </si>
+  <si>
+    <t>1405/01/21</t>
+  </si>
+  <si>
+    <t>مقداد شریفی میناب</t>
+  </si>
+  <si>
+    <t>حواله همراه بانک بابت  ۳۲۷۱۲۳۹۵۴۷</t>
+  </si>
+  <si>
+    <t>سرمایه گذاری نفت برای شرکت</t>
+  </si>
+  <si>
+    <t>طلای آذین</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محسن ایزدپناه </t>
+  </si>
+  <si>
+    <t>؟؟؟؟</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,8 +159,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -169,8 +180,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -195,6 +224,19 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF737373"/>
       </left>
       <right style="thin">
@@ -203,16 +245,15 @@
       <top style="thin">
         <color rgb="FF737373"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF737373"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -226,17 +267,51 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="19" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -515,416 +590,391 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="19" width="9" style="1"/>
-    <col min="20" max="20" width="16.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.125" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="5" t="s">
+      <c r="P1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="5" t="s">
-        <v>13</v>
+      <c r="C2" s="9">
+        <v>0.48063657407407406</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0</v>
+      </c>
+      <c r="G2" s="10">
+        <v>250000450</v>
+      </c>
+      <c r="H2" s="10">
+        <v>441971492</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+    <row r="3" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="3">
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3">
         <v>0.4856597222222222</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2">
-        <v>2402</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1564084318</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="4">
-        <v>300000450</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4">
-        <v>141971042</v>
-      </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2">
-        <v>450</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0.19349537037037037</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2">
-        <v>4481</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>2930415</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="F3" s="14">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>300000450</v>
+      </c>
+      <c r="H3" s="4">
+        <v>141971042</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="11">
+        <v>11</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="11">
+        <v>190</v>
+      </c>
+      <c r="M3" s="11">
+        <v>139</v>
+      </c>
+      <c r="N3" s="11">
+        <v>189</v>
+      </c>
+      <c r="O3" s="11">
+        <v>450</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.19349537037037037</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4">
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="17">
         <v>14300000</v>
       </c>
-      <c r="L3" s="4">
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
         <v>156271042</v>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-    </row>
-    <row r="4" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.21997685185185184</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1503</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>120527481</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4">
-        <v>2860</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>156268182</v>
-      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2">
+      <c r="P4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.21997685185185184</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
         <v>2860</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>30</v>
+      <c r="H5" s="4">
+        <v>156268182</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="11">
+        <v>139</v>
+      </c>
+      <c r="N5" s="11">
+        <v>189</v>
+      </c>
+      <c r="O5" s="11">
+        <v>2860</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
+    <row r="6" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="7">
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="5">
         <v>0.18361111111111111</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="2">
-        <v>4481</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>2193965</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
+      <c r="D6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="16">
         <v>82000000</v>
       </c>
-      <c r="L5" s="2">
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
         <v>238268182</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-    </row>
-    <row r="6" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0.21354166666666666</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1503</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>126341577</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>16400</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
-        <v>238251782</v>
-      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="11">
+        <v>42</v>
+      </c>
+      <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2">
+      <c r="P6" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.21354166666666666</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
         <v>16400</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>30</v>
+      <c r="H7" s="2">
+        <v>238251782</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="11">
+        <v>139</v>
+      </c>
+      <c r="N7" s="11">
+        <v>189</v>
+      </c>
+      <c r="O7" s="11">
+        <v>16400</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+    <row r="8" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="5">
         <v>0.19012731481481482</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4481</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>2329735</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="D8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="16">
         <v>1100000</v>
       </c>
-      <c r="L7" s="2">
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
         <v>239351782</v>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-    </row>
-    <row r="8" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0.22421296296296298</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1503</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>127947617</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1200</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>239350582</v>
-      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="11">
+        <v>84</v>
+      </c>
+      <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
+      <c r="P8" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="11" spans="1:20" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.22421296296296298</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1200</v>
+      </c>
+      <c r="H9" s="2">
+        <v>239350582</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="11">
+        <v>139</v>
+      </c>
+      <c r="N9" s="11">
+        <v>189</v>
+      </c>
+      <c r="O9" s="11">
+        <v>1200</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/حسابداری/بانک ها/ملت/1405/14050201-14050220.xlsx
+++ b/حسابداری/بانک ها/ملت/1405/14050201-14050220.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\ملت\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3545F1D3-DACE-4EEC-B4C1-F511C9F5BE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE9883F-C20E-4A89-BCC9-8272FDF55C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -129,7 +140,7 @@
     <t xml:space="preserve">محسن ایزدپناه </t>
   </si>
   <si>
-    <t>؟؟؟؟</t>
+    <t>واریزی نامشخص</t>
   </si>
 </sst>
 </file>
@@ -253,7 +264,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -307,6 +318,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -599,7 +616,7 @@
     <col min="5" max="5" width="33.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" style="1" customWidth="1"/>
     <col min="9" max="10" width="5.125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.5" style="1" bestFit="1" customWidth="1"/>
@@ -769,7 +786,9 @@
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="18"/>
+      <c r="K4" s="18">
+        <v>135</v>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -973,6 +992,10 @@
       <c r="P9" s="2" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
     </row>
     <row r="12" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>

--- a/حسابداری/بانک ها/ملت/1405/14050201-14050220.xlsx
+++ b/حسابداری/بانک ها/ملت/1405/14050201-14050220.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\ملت\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE9883F-C20E-4A89-BCC9-8272FDF55C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3650DE1C-D8F9-4243-8E6A-68324B751079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -613,7 +613,7 @@
     <col min="1" max="1" width="4.375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9.875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="43.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.75" style="1" customWidth="1"/>
